--- a/resources/templates/Checklist.xlsx
+++ b/resources/templates/Checklist.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="117">
   <si>
     <t>Checklist For Action in the Regional/Field Office</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">SG/Step: </t>
   </si>
   <si>
-    <t>13-1</t>
+    <t>${salary_grade}</t>
   </si>
   <si>
     <t>Monthly Compensation</t>
@@ -237,7 +237,7 @@
     <t xml:space="preserve">         i. Provisional Appointment notation for DepEd </t>
   </si>
   <si>
-    <t>Permanent</t>
+    <t>${employment_status}</t>
   </si>
   <si>
     <t xml:space="preserve">        ii. Is the appointee subject for Probation?
@@ -248,13 +248,10 @@
     <t>Nature of Appointment</t>
   </si>
   <si>
-    <t>Promotion</t>
-  </si>
-  <si>
     <t>Signature of Appointing Authority</t>
   </si>
   <si>
-    <t>August 18, 2025</t>
+    <t>${date_signed}</t>
   </si>
   <si>
     <t>Date of Signing</t>
@@ -1227,18 +1224,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="8.5"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8.5"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8.5"/>
@@ -1285,13 +1280,6 @@
       <color theme="1"/>
       <name val="Bell MT"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1450,6 +1438,14 @@
       <i/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8.5"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2428,146 +2424,146 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="55" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="57" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="57" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="59" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="59" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="60" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="60" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="61" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="61" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="62" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="62" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2836,10 +2832,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2866,14 +2862,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2912,7 +2908,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2930,7 +2926,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2991,7 +2987,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3054,7 +3050,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3069,7 +3065,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3084,7 +3080,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3105,10 +3101,10 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3240,9 +3236,6 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3264,10 +3257,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -3276,13 +3266,13 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3355,7 +3345,7 @@
       <xdr:row>77</xdr:row>
       <xdr:rowOff>15249</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="168166" cy="151711"/>
+    <xdr:ext cx="168166" cy="159331"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1"/>
@@ -3363,8 +3353,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="311150" y="21461730"/>
-          <a:ext cx="168275" cy="151130"/>
+          <a:off x="311150" y="21042630"/>
+          <a:ext cx="168275" cy="158750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3424,7 +3414,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="309880" y="21262975"/>
+          <a:off x="309880" y="20843875"/>
           <a:ext cx="168275" cy="165100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3485,7 +3475,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="309245" y="21114385"/>
+          <a:off x="309245" y="20695285"/>
           <a:ext cx="168275" cy="167005"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3813,14 +3803,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J87"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="13.4259259259259" style="4" customWidth="1"/>
+    <col min="1" max="1" width="13.425" style="4" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="57.712962962963" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.57407407407407" customWidth="1"/>
-    <col min="5" max="5" width="5.71296296296296" customWidth="1"/>
-    <col min="6" max="6" width="4.13888888888889" customWidth="1"/>
+    <col min="3" max="3" width="57.7166666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.575" customWidth="1"/>
+    <col min="5" max="5" width="5.71666666666667" customWidth="1"/>
+    <col min="6" max="6" width="4.14166666666667" customWidth="1"/>
     <col min="7" max="9" width="4" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3890,7 +3880,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="20"/>
-      <c r="F5" s="244" t="s">
+      <c r="F5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="21"/>
@@ -3992,7 +3982,7 @@
       <c r="C11" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="245" t="s">
+      <c r="D11" s="244" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="54"/>
@@ -4013,11 +4003,11 @@
       <c r="C12" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="246" t="s">
+      <c r="D12" s="245" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="62"/>
-      <c r="F12" s="247" t="s">
+      <c r="F12" s="246" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="63"/>
@@ -4032,11 +4022,11 @@
       <c r="C13" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="246" t="s">
+      <c r="D13" s="245" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="62"/>
-      <c r="F13" s="247" t="s">
+      <c r="F13" s="246" t="s">
         <v>30</v>
       </c>
       <c r="G13" s="63"/>
@@ -4051,11 +4041,11 @@
       <c r="C14" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="246" t="s">
+      <c r="D14" s="245" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="61"/>
-      <c r="F14" s="248" t="s">
+      <c r="F14" s="247" t="s">
         <v>33</v>
       </c>
       <c r="G14" s="65"/>
@@ -4095,7 +4085,7 @@
       <c r="I16" s="75"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A17" s="249" t="s">
+      <c r="A17" s="248" t="s">
         <v>37</v>
       </c>
       <c r="B17" s="77">
@@ -4132,7 +4122,7 @@
       <c r="C19" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="250" t="s">
+      <c r="D19" s="249" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="79"/>
@@ -4253,7 +4243,7 @@
         <v>48</v>
       </c>
       <c r="D27" s="95"/>
-      <c r="E27" s="251" t="s">
+      <c r="E27" s="250" t="s">
         <v>26</v>
       </c>
       <c r="F27" s="96" t="s">
@@ -4270,7 +4260,7 @@
         <v>50</v>
       </c>
       <c r="D28" s="100"/>
-      <c r="E28" s="250" t="s">
+      <c r="E28" s="249" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="101" t="s">
@@ -4288,12 +4278,12 @@
       <c r="C29" s="105" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="252" t="s">
+      <c r="D29" s="251" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="107"/>
       <c r="F29" s="108" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G29" s="108"/>
       <c r="H29" s="108"/>
@@ -4305,12 +4295,12 @@
         <v>9</v>
       </c>
       <c r="C30" s="111" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D30" s="106"/>
       <c r="E30" s="107"/>
-      <c r="F30" s="253" t="s">
-        <v>54</v>
+      <c r="F30" s="108" t="s">
+        <v>53</v>
       </c>
       <c r="G30" s="108"/>
       <c r="H30" s="108"/>
@@ -4322,14 +4312,14 @@
         <v>10</v>
       </c>
       <c r="C31" s="111" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="252" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="251" t="s">
         <v>26</v>
       </c>
       <c r="E31" s="107"/>
-      <c r="F31" s="253" t="s">
-        <v>54</v>
+      <c r="F31" s="108" t="s">
+        <v>53</v>
       </c>
       <c r="G31" s="108"/>
       <c r="H31" s="108"/>
@@ -4341,13 +4331,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="113" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="252" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="251" t="s">
         <v>26</v>
       </c>
       <c r="E32" s="106"/>
-      <c r="F32" s="254" t="s">
+      <c r="F32" s="252" t="s">
         <v>35</v>
       </c>
       <c r="G32" s="114"/>
@@ -4360,13 +4350,13 @@
         <v>12</v>
       </c>
       <c r="C33" s="111" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D33" s="106"/>
-      <c r="E33" s="252" t="s">
+      <c r="E33" s="251" t="s">
         <v>26</v>
       </c>
-      <c r="F33" s="255" t="s">
+      <c r="F33" s="253" t="s">
         <v>35</v>
       </c>
       <c r="G33" s="117"/>
@@ -4379,9 +4369,9 @@
         <v>13</v>
       </c>
       <c r="C34" s="119" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="252" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="251" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="106"/>
@@ -4396,9 +4386,9 @@
         <v>14</v>
       </c>
       <c r="C35" s="121" t="s">
-        <v>59</v>
-      </c>
-      <c r="D35" s="256" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="254" t="s">
         <v>26</v>
       </c>
       <c r="E35" s="122"/>
@@ -4411,7 +4401,7 @@
       <c r="A36" s="126"/>
       <c r="B36" s="127"/>
       <c r="C36" s="99" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D36" s="128"/>
       <c r="E36" s="128"/>
@@ -4422,13 +4412,13 @@
     </row>
     <row r="37" s="2" customFormat="1" ht="12" customHeight="1" spans="1:10">
       <c r="A37" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B37" s="93">
         <v>15</v>
       </c>
       <c r="C37" s="78" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D37" s="122" t="s">
         <v>26</v>
@@ -4443,7 +4433,7 @@
       <c r="A38" s="133"/>
       <c r="B38" s="93"/>
       <c r="C38" s="134" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D38" s="128"/>
       <c r="E38" s="128"/>
@@ -4456,10 +4446,10 @@
       <c r="A39" s="133"/>
       <c r="B39" s="98"/>
       <c r="C39" s="138" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D39" s="106"/>
-      <c r="E39" s="252" t="s">
+      <c r="E39" s="251" t="s">
         <v>26</v>
       </c>
       <c r="F39" s="139"/>
@@ -4469,16 +4459,16 @@
     </row>
     <row r="40" s="2" customFormat="1" ht="50.25" customHeight="1" spans="1:10">
       <c r="A40" s="38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B40" s="142">
         <v>16</v>
       </c>
       <c r="C40" s="143" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D40" s="79"/>
-      <c r="E40" s="252" t="s">
+      <c r="E40" s="251" t="s">
         <v>26</v>
       </c>
       <c r="F40" s="144"/>
@@ -4493,10 +4483,10 @@
         <v>17</v>
       </c>
       <c r="C41" s="111" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D41" s="107"/>
-      <c r="E41" s="252" t="s">
+      <c r="E41" s="251" t="s">
         <v>26</v>
       </c>
       <c r="F41" s="144"/>
@@ -4510,7 +4500,7 @@
         <v>18</v>
       </c>
       <c r="C42" s="78" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D42" s="149"/>
       <c r="E42" s="149"/>
@@ -4523,10 +4513,10 @@
       <c r="A43" s="133"/>
       <c r="B43" s="153"/>
       <c r="C43" s="138" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D43" s="79"/>
-      <c r="E43" s="252" t="s">
+      <c r="E43" s="251" t="s">
         <v>26</v>
       </c>
       <c r="F43" s="154"/>
@@ -4540,7 +4530,7 @@
         <v>19</v>
       </c>
       <c r="C44" s="113" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D44" s="149"/>
       <c r="E44" s="149"/>
@@ -4553,10 +4543,10 @@
       <c r="A45" s="133"/>
       <c r="B45" s="158"/>
       <c r="C45" s="134" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D45" s="106"/>
-      <c r="E45" s="252" t="s">
+      <c r="E45" s="251" t="s">
         <v>26</v>
       </c>
       <c r="F45" s="135"/>
@@ -4568,10 +4558,10 @@
       <c r="A46" s="133"/>
       <c r="B46" s="159"/>
       <c r="C46" s="160" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D46" s="106"/>
-      <c r="E46" s="252" t="s">
+      <c r="E46" s="251" t="s">
         <v>26</v>
       </c>
       <c r="F46" s="139"/>
@@ -4585,7 +4575,7 @@
         <v>20</v>
       </c>
       <c r="C47" s="161" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D47" s="88"/>
       <c r="E47" s="122" t="s">
@@ -4602,7 +4592,7 @@
       <c r="A48" s="133"/>
       <c r="B48" s="153"/>
       <c r="C48" s="138" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D48" s="100"/>
       <c r="E48" s="128"/>
@@ -4617,10 +4607,10 @@
         <v>21</v>
       </c>
       <c r="C49" s="162" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D49" s="106"/>
-      <c r="E49" s="252" t="s">
+      <c r="E49" s="251" t="s">
         <v>26</v>
       </c>
       <c r="F49" s="163" t="s">
@@ -4632,16 +4622,16 @@
     </row>
     <row r="50" s="2" customFormat="1" ht="35.25" customHeight="1" spans="1:9">
       <c r="A50" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B50" s="164">
         <v>22</v>
       </c>
       <c r="C50" s="111" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D50" s="106"/>
-      <c r="E50" s="252" t="s">
+      <c r="E50" s="251" t="s">
         <v>26</v>
       </c>
       <c r="F50" s="163" t="s">
@@ -4657,10 +4647,10 @@
         <v>23</v>
       </c>
       <c r="C51" s="165" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D51" s="106"/>
-      <c r="E51" s="252" t="s">
+      <c r="E51" s="251" t="s">
         <v>26</v>
       </c>
       <c r="F51" s="166" t="s">
@@ -4676,7 +4666,7 @@
         <v>24</v>
       </c>
       <c r="C52" s="113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D52" s="149"/>
       <c r="E52" s="170"/>
@@ -4689,7 +4679,7 @@
       <c r="A53" s="133"/>
       <c r="B53" s="148"/>
       <c r="C53" s="174" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D53" s="106"/>
       <c r="E53" s="175"/>
@@ -4704,7 +4694,7 @@
       <c r="A54" s="133"/>
       <c r="B54" s="148"/>
       <c r="C54" s="174" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D54" s="106"/>
       <c r="E54" s="175"/>
@@ -4717,7 +4707,7 @@
       <c r="A55" s="133"/>
       <c r="B55" s="148"/>
       <c r="C55" s="174" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D55" s="106"/>
       <c r="E55" s="175"/>
@@ -4730,7 +4720,7 @@
       <c r="A56" s="133"/>
       <c r="B56" s="148"/>
       <c r="C56" s="174" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D56" s="106"/>
       <c r="E56" s="175"/>
@@ -4743,7 +4733,7 @@
       <c r="A57" s="133"/>
       <c r="B57" s="148"/>
       <c r="C57" s="174" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D57" s="106"/>
       <c r="E57" s="175"/>
@@ -4756,7 +4746,7 @@
       <c r="A58" s="133"/>
       <c r="B58" s="153"/>
       <c r="C58" s="162" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D58" s="106"/>
       <c r="E58" s="175"/>
@@ -4771,10 +4761,10 @@
         <v>25</v>
       </c>
       <c r="C59" s="174" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D59" s="88"/>
-      <c r="E59" s="257" t="s">
+      <c r="E59" s="255" t="s">
         <v>26</v>
       </c>
       <c r="F59" s="131" t="s">
@@ -4784,11 +4774,11 @@
       <c r="H59" s="131"/>
       <c r="I59" s="132"/>
     </row>
-    <row r="60" s="2" customFormat="1" ht="10.2" spans="1:9">
+    <row r="60" s="2" customFormat="1" ht="10.8" spans="1:9">
       <c r="A60" s="133"/>
       <c r="B60" s="179"/>
       <c r="C60" s="174" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D60" s="100"/>
       <c r="E60" s="100"/>
@@ -4797,14 +4787,14 @@
       <c r="H60" s="136"/>
       <c r="I60" s="137"/>
     </row>
-    <row r="61" s="2" customFormat="1" ht="30.6" spans="1:9">
+    <row r="61" s="2" customFormat="1" ht="21.6" spans="1:9">
       <c r="A61" s="133"/>
       <c r="B61" s="179"/>
       <c r="C61" s="134" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D61" s="180"/>
-      <c r="E61" s="250" t="s">
+      <c r="E61" s="249" t="s">
         <v>26</v>
       </c>
       <c r="F61" s="136"/>
@@ -4812,14 +4802,14 @@
       <c r="H61" s="136"/>
       <c r="I61" s="137"/>
     </row>
-    <row r="62" s="2" customFormat="1" ht="30.6" spans="1:9">
+    <row r="62" s="2" customFormat="1" ht="21.6" spans="1:9">
       <c r="A62" s="133"/>
       <c r="B62" s="181"/>
       <c r="C62" s="134" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D62" s="180"/>
-      <c r="E62" s="250" t="s">
+      <c r="E62" s="249" t="s">
         <v>26</v>
       </c>
       <c r="F62" s="136"/>
@@ -4833,10 +4823,10 @@
         <v>26</v>
       </c>
       <c r="C63" s="113" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D63" s="88"/>
-      <c r="E63" s="257" t="s">
+      <c r="E63" s="255" t="s">
         <v>26</v>
       </c>
       <c r="F63" s="182"/>
@@ -4848,7 +4838,7 @@
       <c r="A64" s="133"/>
       <c r="B64" s="148"/>
       <c r="C64" s="138" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D64" s="100"/>
       <c r="E64" s="100"/>
@@ -4863,10 +4853,10 @@
         <v>27</v>
       </c>
       <c r="C65" s="185" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D65" s="79"/>
-      <c r="E65" s="250" t="s">
+      <c r="E65" s="249" t="s">
         <v>26</v>
       </c>
       <c r="F65" s="182"/>
@@ -4874,17 +4864,17 @@
       <c r="H65" s="183"/>
       <c r="I65" s="184"/>
     </row>
-    <row r="66" s="2" customFormat="1" ht="40.8" spans="1:9">
+    <row r="66" s="2" customFormat="1" ht="32.4" spans="1:9">
       <c r="A66" s="38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B66" s="186">
         <v>28</v>
       </c>
       <c r="C66" s="162" t="s">
-        <v>94</v>
-      </c>
-      <c r="D66" s="258" t="s">
+        <v>93</v>
+      </c>
+      <c r="D66" s="256" t="s">
         <v>26</v>
       </c>
       <c r="E66" s="188"/>
@@ -4899,9 +4889,9 @@
         <v>29</v>
       </c>
       <c r="C67" s="193" t="s">
-        <v>95</v>
-      </c>
-      <c r="D67" s="258" t="s">
+        <v>94</v>
+      </c>
+      <c r="D67" s="256" t="s">
         <v>26</v>
       </c>
       <c r="E67" s="187"/>
@@ -4916,9 +4906,9 @@
         <v>30</v>
       </c>
       <c r="C68" s="193" t="s">
-        <v>96</v>
-      </c>
-      <c r="D68" s="258" t="s">
+        <v>95</v>
+      </c>
+      <c r="D68" s="256" t="s">
         <v>26</v>
       </c>
       <c r="E68" s="187"/>
@@ -4933,9 +4923,9 @@
         <v>31</v>
       </c>
       <c r="C69" s="111" t="s">
-        <v>97</v>
-      </c>
-      <c r="D69" s="258" t="s">
+        <v>96</v>
+      </c>
+      <c r="D69" s="256" t="s">
         <v>26</v>
       </c>
       <c r="E69" s="187"/>
@@ -4950,9 +4940,9 @@
         <v>32</v>
       </c>
       <c r="C70" s="111" t="s">
-        <v>98</v>
-      </c>
-      <c r="D70" s="258" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" s="256" t="s">
         <v>26</v>
       </c>
       <c r="E70" s="107"/>
@@ -4967,7 +4957,7 @@
         <v>33</v>
       </c>
       <c r="C71" s="193" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D71" s="107"/>
       <c r="E71" s="107"/>
@@ -4978,13 +4968,13 @@
       <c r="H71" s="144"/>
       <c r="I71" s="145"/>
     </row>
-    <row r="72" s="2" customFormat="1" ht="61.2" spans="1:9">
+    <row r="72" s="2" customFormat="1" ht="54" spans="1:9">
       <c r="A72" s="133"/>
       <c r="B72" s="194">
         <v>34</v>
       </c>
       <c r="C72" s="195" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D72" s="107"/>
       <c r="E72" s="107"/>
@@ -4999,7 +4989,7 @@
         <v>35</v>
       </c>
       <c r="C73" s="197" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D73" s="198"/>
       <c r="E73" s="198"/>
@@ -5008,9 +4998,9 @@
       <c r="H73" s="200"/>
       <c r="I73" s="201"/>
     </row>
-    <row r="74" s="2" customFormat="1" ht="10.95" spans="1:9">
+    <row r="74" s="2" customFormat="1" ht="11.55" spans="1:9">
       <c r="A74" s="202" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B74" s="203"/>
       <c r="C74" s="204"/>
@@ -5034,21 +5024,21 @@
     </row>
     <row r="76" s="2" customFormat="1" ht="11.4" spans="1:9">
       <c r="A76" s="211" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B76" s="212"/>
       <c r="I76" s="213"/>
     </row>
     <row r="77" s="2" customFormat="1" ht="15.75" customHeight="1" spans="1:9">
       <c r="A77" s="214" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B77" s="203"/>
       <c r="I77" s="213"/>
     </row>
-    <row r="78" s="2" customFormat="1" ht="10.2" spans="1:9">
+    <row r="78" s="2" customFormat="1" ht="10.8" spans="1:9">
       <c r="A78" s="214" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B78" s="203"/>
       <c r="C78" s="215"/>
@@ -5061,7 +5051,7 @@
     </row>
     <row r="79" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
       <c r="A79" s="216" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B79" s="217"/>
       <c r="F79" s="218"/>
@@ -5091,16 +5081,16 @@
       <c r="H81" s="222"/>
       <c r="I81" s="223"/>
     </row>
-    <row r="82" s="2" customFormat="1" ht="10.2" spans="1:10">
+    <row r="82" s="2" customFormat="1" ht="10.8" spans="1:10">
       <c r="A82" s="224" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B82" s="207"/>
       <c r="C82" s="224" t="s">
+        <v>107</v>
+      </c>
+      <c r="D82" s="224" t="s">
         <v>108</v>
-      </c>
-      <c r="D82" s="224" t="s">
-        <v>109</v>
       </c>
       <c r="E82" s="208"/>
       <c r="F82" s="208"/>
@@ -5121,15 +5111,15 @@
     </row>
     <row r="84" s="2" customFormat="1" ht="15" customHeight="1" spans="1:10">
       <c r="A84" s="228" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B84" s="229"/>
       <c r="C84" s="228" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D84" s="216"/>
       <c r="E84" s="230" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F84" s="230"/>
       <c r="G84" s="230"/>
@@ -5139,14 +5129,14 @@
     </row>
     <row r="85" s="3" customFormat="1" ht="14.25" customHeight="1" spans="1:10">
       <c r="A85" s="233" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B85" s="234"/>
       <c r="C85" s="233" t="s">
+        <v>113</v>
+      </c>
+      <c r="D85" s="233" t="s">
         <v>114</v>
-      </c>
-      <c r="D85" s="233" t="s">
-        <v>115</v>
       </c>
       <c r="E85" s="235"/>
       <c r="F85" s="235"/>
@@ -5156,14 +5146,14 @@
     </row>
     <row r="86" s="3" customFormat="1" ht="14.25" customHeight="1" spans="1:10">
       <c r="A86" s="236" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B86" s="237"/>
       <c r="C86" s="238" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D86" s="239" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E86" s="240"/>
       <c r="F86" s="240"/>
@@ -5173,7 +5163,7 @@
     </row>
     <row r="87" s="2" customFormat="1" ht="12.75" customHeight="1" spans="1:10">
       <c r="A87" s="242" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B87" s="243"/>
     </row>

--- a/resources/templates/Checklist.xlsx
+++ b/resources/templates/Checklist.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,12 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="118">
   <si>
     <t>Checklist For Action in the Regional/Field Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>APPOINTMENT PROCESSING CHECKLIST</t>
@@ -111,25 +108,25 @@
     <t>/</t>
   </si>
   <si>
-    <t>Bachelor of Secondary Education major in English</t>
+    <t>${education}</t>
   </si>
   <si>
     <t>Does the appointee meet the minimum qualification requirements of the position at the time of issuance of appointment?</t>
   </si>
   <si>
-    <t>Experience:   2 years teaching experience</t>
+    <t>Experience:   None Required</t>
   </si>
   <si>
     <t>pls. see attached</t>
   </si>
   <si>
-    <t>Training: 16 hours of training in any of or cumulative of the following: Curriculum, Pedagogy, Subject especialization acquired within the last 5 years</t>
+    <t>Training:  None Required</t>
   </si>
   <si>
     <t>Eligibility: RA 1080, as amended (Teacher- Elementary/Secondary)</t>
   </si>
   <si>
-    <t>LET</t>
+    <t>${eligibility}</t>
   </si>
   <si>
     <r>
@@ -181,16 +178,19 @@
     </r>
   </si>
   <si>
+    <t>${strand}</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
     <t>Original Copy/ies of Appointment (3 copies)</t>
   </si>
   <si>
-    <t xml:space="preserve">          i. CS Form No. 33-A Revised 2018 Appointment Form (Regulated)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          ii. CS Form No. 33-B Revised 2018 Appointment Form (Accredited)</t>
+    <t xml:space="preserve">          i. CS Form No. 33-A Revised 2025 Appointment Form (Regulated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          ii. CS Form No. 33-B Revised 2025 Appointment Form (Accredited)</t>
   </si>
   <si>
     <t xml:space="preserve">          iii. CS Form No. 34-A Plantilla of Casual Appointment (Regulated)</t>
@@ -248,13 +248,16 @@
     <t>Nature of Appointment</t>
   </si>
   <si>
+    <t>${appointment_nature}</t>
+  </si>
+  <si>
     <t>Signature of Appointing Authority</t>
   </si>
   <si>
-    <t>${date_signed}</t>
-  </si>
-  <si>
     <t>Date of Signing</t>
+  </si>
+  <si>
+    <t>${date_of_signing}</t>
   </si>
   <si>
     <r>
@@ -279,6 +282,9 @@
       </rPr>
       <t xml:space="preserve">                                                                                 (should be duly signed by the authorized HRMO)</t>
     </r>
+  </si>
+  <si>
+    <t>${publication_date_from}</t>
   </si>
   <si>
     <r>
@@ -385,7 +391,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 2017)</t>
+      <t xml:space="preserve"> 2025)</t>
     </r>
   </si>
   <si>
@@ -399,10 +405,10 @@
     <t>Is the agency accredited?</t>
   </si>
   <si>
-    <t xml:space="preserve">          i.  If accredited, was RAI (CS Form No.  2, Revised 2018) with original copy of appointment (CSC copy) and supporting documents submitted to the CSC on or before the 30th day of the succeeding month?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        ii.  If NOT accredited, was the appointment (3 copies) submitted to the CSC with supporting documents in the prescribed Appointment Transmittal Form (CS Form No. 1, Revised 2018) within 30 calendar days from the date of issuance?</t>
+    <t xml:space="preserve">          i.  If accredited, was RAI (CS Form No.  2, Revised 2025) with original copy of appointment (CSC copy) and supporting documents submitted to the CSC on or before the 30th day of the succeeding month?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        ii.  If NOT accredited, was the appointment (3 copies) submitted to the CSC with supporting documents in the prescribed Appointment Transmittal Form (CS Form No. 1, Revised 2025) within 30 calendar days from the date of issuance?</t>
   </si>
   <si>
     <r>
@@ -932,7 +938,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(CS Form No. 32, Revised 2018)</t>
+      <t>(CS Form No. 32, Revised 2025)</t>
     </r>
   </si>
   <si>
@@ -957,7 +963,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(CS Form No. 4, Revised 2018)</t>
+      <t>(CS Form No. 4, Revised 2025)</t>
     </r>
   </si>
   <si>
@@ -991,9 +997,9 @@
   <si>
     <t>Electronic file stored in CD/flash drive or sent thru email + 2 printed copies of:
       i. Appointment Transmittal and Action Form (ATAF)
-          (CS Form No. 1 rev. 2018) or 
+          (CS Form No. 1 rev. 2025) or 
      ii. Reports on Appointment Issued (RAI)
-         (CS Form No. 2 rev. 2018)</t>
+         (CS Form No. 2 rev. 2025)</t>
   </si>
   <si>
     <t>Others:</t>
@@ -1023,16 +1029,16 @@
     <t>Recommended:</t>
   </si>
   <si>
-    <t>MA. CORAZON P. FEDEROSO</t>
-  </si>
-  <si>
-    <t>RONALD KEVIN C. DEL ROSARIO</t>
+    <t>${encoder_name}</t>
+  </si>
+  <si>
+    <t>GHAYLORD P. ANCIANO</t>
   </si>
   <si>
     <t>VERNA C. CABAYA</t>
   </si>
   <si>
-    <t>Administrative Assistant III</t>
+    <t>${user_position}</t>
   </si>
   <si>
     <t>Administrative Officer IV-HR</t>
@@ -1041,10 +1047,7 @@
     <t>Administrative Officer V</t>
   </si>
   <si>
-    <t>Date: February 19, 2025</t>
-  </si>
-  <si>
-    <t>APC Form - (Revised 2018)</t>
+    <t>Date: ${date_of_signing}</t>
   </si>
 </sst>
 </file>
@@ -1058,7 +1061,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="dd\-mmm\-yy"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="49">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1182,7 +1185,7 @@
     </font>
     <font>
       <sz val="7"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1190,21 +1193,6 @@
     <font>
       <i/>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1228,12 +1216,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8.5"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8.5"/>
@@ -1426,6 +1408,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="8.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <i/>
       <sz val="8.5"/>
@@ -1438,14 +1428,6 @@
       <i/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8.5"/>
-      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2439,135 +2421,135 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="55" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="57" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="59" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="57" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="60" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="61" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="59" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="62" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="60" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="61" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="62" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2741,12 +2723,6 @@
     <xf numFmtId="176" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2768,13 +2744,13 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2792,7 +2768,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2811,7 +2787,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2832,10 +2808,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2862,14 +2838,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2878,18 +2854,18 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2908,7 +2884,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2920,13 +2896,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2980,14 +2956,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3023,7 +2999,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3050,7 +3026,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3065,7 +3041,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3080,7 +3056,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3101,10 +3077,10 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3157,8 +3133,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3192,17 +3168,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3214,26 +3190,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -3245,10 +3221,7 @@
     <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -3257,22 +3230,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3508,6 +3478,483 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-PH" sz="1100">
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>311604</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>15249</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="168166" cy="166951"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="311150" y="21042630"/>
+          <a:ext cx="168275" cy="166370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:endParaRPr lang="en-PH" sz="1100">
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>310267</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>17009</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="168166" cy="165046"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 2"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="309880" y="20843875"/>
+          <a:ext cx="168275" cy="165100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:endParaRPr lang="en-PH" sz="1100">
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>309587</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>12927</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="168166" cy="166951"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 3"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="309245" y="20695285"/>
+          <a:ext cx="168275" cy="167005"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="en-US">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
         <a:p>
           <a:endParaRPr lang="en-PH" sz="1100">
             <a:ln>
@@ -3822,18 +4269,14 @@
         <v>0</v>
       </c>
       <c r="E1" s="8"/>
-      <c r="F1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>1</v>
-      </c>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:9">
       <c r="A2" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -3855,10 +4298,10 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:9">
       <c r="A4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>3</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>4</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -3870,18 +4313,18 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:9">
       <c r="A5" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>5</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>6</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="20"/>
       <c r="F5" s="21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="21"/>
@@ -3889,14 +4332,14 @@
     </row>
     <row r="6" s="1" customFormat="1" ht="24" customHeight="1" spans="1:9">
       <c r="A6" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>9</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="C6" s="24"/>
       <c r="D6" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
@@ -3906,27 +4349,27 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:9">
       <c r="A7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>13</v>
       </c>
       <c r="C7" s="32"/>
       <c r="D7" s="33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="H7" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="34" t="s">
+      <c r="I7" s="35" t="s">
         <v>17</v>
-      </c>
-      <c r="I7" s="35" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" ht="4.5" customHeight="1" spans="1:9">
@@ -3942,20 +4385,20 @@
     </row>
     <row r="9" s="2" customFormat="1" ht="15" customHeight="1" spans="1:9">
       <c r="A9" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="39" t="s">
         <v>19</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>20</v>
       </c>
       <c r="C9" s="39"/>
       <c r="D9" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="F9" s="42" t="s">
         <v>22</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>23</v>
       </c>
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
@@ -3974,20 +4417,20 @@
     </row>
     <row r="11" s="2" customFormat="1" ht="55.15" customHeight="1" spans="1:9">
       <c r="A11" s="50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="51">
         <v>1</v>
       </c>
       <c r="C11" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="242" t="s">
         <v>25</v>
-      </c>
-      <c r="D11" s="244" t="s">
-        <v>26</v>
       </c>
       <c r="E11" s="54"/>
       <c r="F11" s="55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" s="56"/>
       <c r="H11" s="56"/>
@@ -3995,20 +4438,20 @@
     </row>
     <row r="12" s="2" customFormat="1" ht="14.1" customHeight="1" spans="1:9">
       <c r="A12" s="58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="59">
         <v>2</v>
       </c>
       <c r="C12" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="243" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="62"/>
+      <c r="F12" s="244" t="s">
         <v>29</v>
-      </c>
-      <c r="D12" s="245" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="62"/>
-      <c r="F12" s="246" t="s">
-        <v>30</v>
       </c>
       <c r="G12" s="63"/>
       <c r="H12" s="63"/>
@@ -4020,14 +4463,14 @@
         <v>3</v>
       </c>
       <c r="C13" s="60" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="245" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="D13" s="243" t="s">
+        <v>25</v>
       </c>
       <c r="E13" s="62"/>
-      <c r="F13" s="246" t="s">
-        <v>30</v>
+      <c r="F13" s="244" t="s">
+        <v>29</v>
       </c>
       <c r="G13" s="63"/>
       <c r="H13" s="63"/>
@@ -4039,1133 +4482,1135 @@
         <v>4</v>
       </c>
       <c r="C14" s="60" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="243" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="61"/>
+      <c r="F14" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="245" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="61"/>
-      <c r="F14" s="247" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="66"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="64"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="25.5" customHeight="1" spans="1:9">
       <c r="A15" s="58"/>
-      <c r="B15" s="67">
+      <c r="B15" s="65">
         <v>5</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="70" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="72"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="70"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A16" s="73"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="51"/>
       <c r="C16" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="75"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="73"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A17" s="248" t="s">
+      <c r="A17" s="245" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="77">
+      <c r="B17" s="75">
         <v>6</v>
       </c>
-      <c r="C17" s="78" t="s">
+      <c r="C17" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="81"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="79"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A18" s="82"/>
-      <c r="B18" s="83"/>
-      <c r="C18" s="84" t="s">
+      <c r="A18" s="80"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="85" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="86"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="84"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A19" s="82"/>
-      <c r="B19" s="83"/>
-      <c r="C19" s="87" t="s">
+      <c r="A19" s="80"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="249" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="79"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="86"/>
+      <c r="D19" s="246" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="77"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="84"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A20" s="82"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="87" t="s">
+      <c r="A20" s="80"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="85" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="86"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="84"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A21" s="82"/>
-      <c r="B21" s="83"/>
-      <c r="C21" s="87" t="s">
+      <c r="A21" s="80"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="85" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="85"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="86"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="83"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="84"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A22" s="82"/>
-      <c r="B22" s="83"/>
-      <c r="C22" s="87" t="s">
+      <c r="A22" s="80"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="85" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="86"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="83"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="84"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A23" s="82"/>
-      <c r="B23" s="83"/>
-      <c r="C23" s="87" t="s">
+      <c r="A23" s="80"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="85" t="s">
-        <v>35</v>
-      </c>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="86"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="84"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A24" s="82"/>
-      <c r="B24" s="83"/>
-      <c r="C24" s="87" t="s">
+      <c r="A24" s="80"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="85" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" s="85"/>
-      <c r="H24" s="85"/>
-      <c r="I24" s="86"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="84"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A25" s="82"/>
-      <c r="B25" s="83"/>
-      <c r="C25" s="87" t="s">
+      <c r="A25" s="80"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="88"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="85" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="84"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A26" s="89"/>
-      <c r="B26" s="90">
+      <c r="A26" s="87"/>
+      <c r="B26" s="88">
         <v>7</v>
       </c>
-      <c r="C26" s="91" t="s">
+      <c r="C26" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="92"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="80"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="81"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="79"/>
     </row>
     <row r="27" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A27" s="89"/>
-      <c r="B27" s="93"/>
-      <c r="C27" s="94" t="s">
+      <c r="A27" s="87"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="95"/>
-      <c r="E27" s="250" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" s="96" t="s">
+      <c r="D27" s="93"/>
+      <c r="E27" s="247" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="G27" s="96"/>
-      <c r="H27" s="96"/>
-      <c r="I27" s="97"/>
+      <c r="G27" s="94"/>
+      <c r="H27" s="94"/>
+      <c r="I27" s="95"/>
     </row>
     <row r="28" s="2" customFormat="1" ht="39.75" customHeight="1" spans="1:9">
-      <c r="A28" s="89"/>
-      <c r="B28" s="98"/>
-      <c r="C28" s="99" t="s">
+      <c r="A28" s="87"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="100"/>
-      <c r="E28" s="249" t="s">
-        <v>26</v>
-      </c>
-      <c r="F28" s="101" t="s">
-        <v>35</v>
-      </c>
-      <c r="G28" s="102"/>
-      <c r="H28" s="102"/>
-      <c r="I28" s="103"/>
+      <c r="D28" s="98"/>
+      <c r="E28" s="246" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="100"/>
+      <c r="H28" s="100"/>
+      <c r="I28" s="101"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A29" s="82"/>
-      <c r="B29" s="104">
+      <c r="A29" s="80"/>
+      <c r="B29" s="102">
         <v>8</v>
       </c>
-      <c r="C29" s="105" t="s">
+      <c r="C29" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="107"/>
-      <c r="F29" s="108" t="s">
-        <v>35</v>
-      </c>
-      <c r="G29" s="108"/>
-      <c r="H29" s="108"/>
-      <c r="I29" s="109"/>
+      <c r="D29" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="105"/>
+      <c r="F29" s="106" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="106"/>
+      <c r="H29" s="106"/>
+      <c r="I29" s="107"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A30" s="82"/>
-      <c r="B30" s="110">
+      <c r="A30" s="80"/>
+      <c r="B30" s="108">
         <v>9</v>
       </c>
-      <c r="C30" s="111" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="106"/>
-      <c r="E30" s="107"/>
-      <c r="F30" s="108" t="s">
+      <c r="C30" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="G30" s="108"/>
-      <c r="H30" s="108"/>
-      <c r="I30" s="109"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="110" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" s="110"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="111"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A31" s="82"/>
-      <c r="B31" s="110">
+      <c r="A31" s="80"/>
+      <c r="B31" s="108">
         <v>10</v>
       </c>
-      <c r="C31" s="111" t="s">
+      <c r="C31" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="107"/>
-      <c r="F31" s="108" t="s">
-        <v>53</v>
-      </c>
-      <c r="G31" s="108"/>
-      <c r="H31" s="108"/>
-      <c r="I31" s="109"/>
+      <c r="D31" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="105"/>
+      <c r="F31" s="106" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="106"/>
+      <c r="H31" s="106"/>
+      <c r="I31" s="107"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="24" customHeight="1" spans="1:9">
-      <c r="A32" s="82"/>
+      <c r="A32" s="80"/>
       <c r="B32" s="112">
         <v>11</v>
       </c>
       <c r="C32" s="113" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="106"/>
-      <c r="F32" s="252" t="s">
-        <v>35</v>
-      </c>
-      <c r="G32" s="114"/>
-      <c r="H32" s="114"/>
-      <c r="I32" s="115"/>
+        <v>56</v>
+      </c>
+      <c r="D32" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="104"/>
+      <c r="F32" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="106"/>
+      <c r="H32" s="106"/>
+      <c r="I32" s="107"/>
     </row>
     <row r="33" s="2" customFormat="1" ht="24" customHeight="1" spans="1:10">
-      <c r="A33" s="82"/>
-      <c r="B33" s="110">
+      <c r="A33" s="80"/>
+      <c r="B33" s="108">
         <v>12</v>
       </c>
-      <c r="C33" s="111" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" s="106"/>
-      <c r="E33" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="F33" s="253" t="s">
-        <v>35</v>
-      </c>
-      <c r="G33" s="117"/>
-      <c r="H33" s="117"/>
-      <c r="I33" s="118"/>
+      <c r="C33" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="104"/>
+      <c r="E33" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="249" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" s="115"/>
+      <c r="H33" s="115"/>
+      <c r="I33" s="116"/>
     </row>
     <row r="34" s="2" customFormat="1" ht="33.75" customHeight="1" spans="1:10">
-      <c r="A34" s="82"/>
-      <c r="B34" s="110">
+      <c r="A34" s="80"/>
+      <c r="B34" s="108">
         <v>13</v>
       </c>
-      <c r="C34" s="119" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="106"/>
-      <c r="F34" s="80"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="81"/>
+      <c r="C34" s="117" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="104"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="78"/>
+      <c r="I34" s="79"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A35" s="82"/>
-      <c r="B35" s="120">
+      <c r="A35" s="80"/>
+      <c r="B35" s="118">
         <v>14</v>
       </c>
-      <c r="C35" s="121" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" s="254" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="122"/>
-      <c r="F35" s="123"/>
-      <c r="G35" s="124"/>
-      <c r="H35" s="124"/>
-      <c r="I35" s="125"/>
+      <c r="C35" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="250" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="120"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="122"/>
+      <c r="I35" s="123"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="24.95" customHeight="1" spans="1:10">
-      <c r="A36" s="126"/>
-      <c r="B36" s="127"/>
-      <c r="C36" s="99" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="128"/>
-      <c r="E36" s="128"/>
-      <c r="F36" s="129"/>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="81"/>
+      <c r="A36" s="124"/>
+      <c r="B36" s="125"/>
+      <c r="C36" s="97" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="126"/>
+      <c r="E36" s="126"/>
+      <c r="F36" s="127"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="78"/>
+      <c r="I36" s="79"/>
     </row>
     <row r="37" s="2" customFormat="1" ht="12" customHeight="1" spans="1:10">
       <c r="A37" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" s="93">
+        <v>62</v>
+      </c>
+      <c r="B37" s="91">
         <v>15</v>
       </c>
-      <c r="C37" s="78" t="s">
-        <v>61</v>
-      </c>
-      <c r="D37" s="122" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" s="122"/>
-      <c r="F37" s="130"/>
-      <c r="G37" s="131"/>
-      <c r="H37" s="131"/>
-      <c r="I37" s="132"/>
+      <c r="C37" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="120" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="120"/>
+      <c r="F37" s="128"/>
+      <c r="G37" s="129"/>
+      <c r="H37" s="129"/>
+      <c r="I37" s="130"/>
     </row>
     <row r="38" s="2" customFormat="1" ht="40.5" customHeight="1" spans="1:10">
-      <c r="A38" s="133"/>
-      <c r="B38" s="93"/>
-      <c r="C38" s="134" t="s">
-        <v>62</v>
-      </c>
-      <c r="D38" s="128"/>
-      <c r="E38" s="128"/>
-      <c r="F38" s="135"/>
-      <c r="G38" s="136"/>
-      <c r="H38" s="136"/>
-      <c r="I38" s="137"/>
+      <c r="A38" s="131"/>
+      <c r="B38" s="91"/>
+      <c r="C38" s="132" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="126"/>
+      <c r="E38" s="126"/>
+      <c r="F38" s="133"/>
+      <c r="G38" s="134"/>
+      <c r="H38" s="134"/>
+      <c r="I38" s="135"/>
     </row>
     <row r="39" s="2" customFormat="1" ht="33" customHeight="1" spans="1:10">
-      <c r="A39" s="133"/>
-      <c r="B39" s="98"/>
-      <c r="C39" s="138" t="s">
-        <v>63</v>
-      </c>
-      <c r="D39" s="106"/>
-      <c r="E39" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="F39" s="139"/>
-      <c r="G39" s="140"/>
-      <c r="H39" s="140"/>
-      <c r="I39" s="141"/>
+      <c r="A39" s="131"/>
+      <c r="B39" s="96"/>
+      <c r="C39" s="136" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="104"/>
+      <c r="E39" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="137"/>
+      <c r="G39" s="138"/>
+      <c r="H39" s="138"/>
+      <c r="I39" s="139"/>
     </row>
     <row r="40" s="2" customFormat="1" ht="50.25" customHeight="1" spans="1:10">
       <c r="A40" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="B40" s="142">
+        <v>66</v>
+      </c>
+      <c r="B40" s="140">
         <v>16</v>
       </c>
-      <c r="C40" s="143" t="s">
-        <v>65</v>
-      </c>
-      <c r="D40" s="79"/>
-      <c r="E40" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="F40" s="144"/>
-      <c r="G40" s="144"/>
-      <c r="H40" s="144"/>
-      <c r="I40" s="145"/>
-      <c r="J40" s="146"/>
+      <c r="C40" s="141" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="77"/>
+      <c r="E40" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="142"/>
+      <c r="G40" s="142"/>
+      <c r="H40" s="142"/>
+      <c r="I40" s="143"/>
+      <c r="J40" s="144"/>
     </row>
     <row r="41" s="2" customFormat="1" ht="24" customHeight="1" spans="1:10">
-      <c r="A41" s="133"/>
-      <c r="B41" s="147">
+      <c r="A41" s="131"/>
+      <c r="B41" s="145">
         <v>17</v>
       </c>
-      <c r="C41" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="D41" s="107"/>
-      <c r="E41" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="F41" s="144"/>
-      <c r="G41" s="144"/>
-      <c r="H41" s="144"/>
-      <c r="I41" s="145"/>
+      <c r="C41" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="105"/>
+      <c r="E41" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="142"/>
+      <c r="G41" s="142"/>
+      <c r="H41" s="142"/>
+      <c r="I41" s="143"/>
     </row>
     <row r="42" s="2" customFormat="1" ht="12" customHeight="1" spans="1:10">
-      <c r="A42" s="133"/>
-      <c r="B42" s="148">
+      <c r="A42" s="131"/>
+      <c r="B42" s="146">
         <v>18</v>
       </c>
-      <c r="C42" s="78" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42" s="149"/>
-      <c r="E42" s="149"/>
-      <c r="F42" s="150"/>
-      <c r="G42" s="151"/>
-      <c r="H42" s="151"/>
-      <c r="I42" s="152"/>
+      <c r="C42" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" s="147"/>
+      <c r="E42" s="147"/>
+      <c r="F42" s="148"/>
+      <c r="G42" s="149"/>
+      <c r="H42" s="149"/>
+      <c r="I42" s="150"/>
     </row>
     <row r="43" s="2" customFormat="1" ht="27.75" customHeight="1" spans="1:10">
-      <c r="A43" s="133"/>
-      <c r="B43" s="153"/>
-      <c r="C43" s="138" t="s">
-        <v>68</v>
-      </c>
-      <c r="D43" s="79"/>
-      <c r="E43" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="F43" s="154"/>
-      <c r="G43" s="155"/>
-      <c r="H43" s="155"/>
-      <c r="I43" s="156"/>
+      <c r="A43" s="131"/>
+      <c r="B43" s="151"/>
+      <c r="C43" s="136" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="77"/>
+      <c r="E43" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="152"/>
+      <c r="G43" s="153"/>
+      <c r="H43" s="153"/>
+      <c r="I43" s="154"/>
     </row>
     <row r="44" s="2" customFormat="1" ht="12" customHeight="1" spans="1:10">
-      <c r="A44" s="133"/>
-      <c r="B44" s="157">
+      <c r="A44" s="131"/>
+      <c r="B44" s="155">
         <v>19</v>
       </c>
       <c r="C44" s="113" t="s">
-        <v>69</v>
-      </c>
-      <c r="D44" s="149"/>
-      <c r="E44" s="149"/>
-      <c r="F44" s="130"/>
-      <c r="G44" s="131"/>
-      <c r="H44" s="131"/>
-      <c r="I44" s="132"/>
+        <v>71</v>
+      </c>
+      <c r="D44" s="147"/>
+      <c r="E44" s="147"/>
+      <c r="F44" s="128"/>
+      <c r="G44" s="129"/>
+      <c r="H44" s="129"/>
+      <c r="I44" s="130"/>
     </row>
     <row r="45" s="2" customFormat="1" ht="33" customHeight="1" spans="1:10">
-      <c r="A45" s="133"/>
-      <c r="B45" s="158"/>
-      <c r="C45" s="134" t="s">
-        <v>70</v>
-      </c>
-      <c r="D45" s="106"/>
-      <c r="E45" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="F45" s="135"/>
-      <c r="G45" s="136"/>
-      <c r="H45" s="136"/>
-      <c r="I45" s="137"/>
+      <c r="A45" s="131"/>
+      <c r="B45" s="156"/>
+      <c r="C45" s="132" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" s="104"/>
+      <c r="E45" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="133"/>
+      <c r="G45" s="134"/>
+      <c r="H45" s="134"/>
+      <c r="I45" s="135"/>
     </row>
     <row r="46" s="2" customFormat="1" ht="24" customHeight="1" spans="1:10">
-      <c r="A46" s="133"/>
-      <c r="B46" s="159"/>
-      <c r="C46" s="160" t="s">
-        <v>71</v>
-      </c>
-      <c r="D46" s="106"/>
-      <c r="E46" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="F46" s="139"/>
-      <c r="G46" s="140"/>
-      <c r="H46" s="140"/>
-      <c r="I46" s="141"/>
+      <c r="A46" s="131"/>
+      <c r="B46" s="157"/>
+      <c r="C46" s="158" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" s="104"/>
+      <c r="E46" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="137"/>
+      <c r="G46" s="138"/>
+      <c r="H46" s="138"/>
+      <c r="I46" s="139"/>
     </row>
     <row r="47" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A47" s="133"/>
-      <c r="B47" s="148">
+      <c r="A47" s="131"/>
+      <c r="B47" s="146">
         <v>20</v>
       </c>
-      <c r="C47" s="161" t="s">
-        <v>72</v>
-      </c>
-      <c r="D47" s="88"/>
-      <c r="E47" s="122" t="s">
-        <v>26</v>
-      </c>
-      <c r="F47" s="130" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" s="131"/>
-      <c r="H47" s="131"/>
-      <c r="I47" s="132"/>
+      <c r="C47" s="159" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" s="86"/>
+      <c r="E47" s="120" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="128" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" s="129"/>
+      <c r="H47" s="129"/>
+      <c r="I47" s="130"/>
     </row>
     <row r="48" s="2" customFormat="1" ht="22.5" customHeight="1" spans="1:10">
-      <c r="A48" s="133"/>
-      <c r="B48" s="153"/>
-      <c r="C48" s="138" t="s">
-        <v>73</v>
-      </c>
-      <c r="D48" s="100"/>
-      <c r="E48" s="128"/>
-      <c r="F48" s="139"/>
-      <c r="G48" s="140"/>
-      <c r="H48" s="140"/>
-      <c r="I48" s="141"/>
+      <c r="A48" s="131"/>
+      <c r="B48" s="151"/>
+      <c r="C48" s="136" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" s="98"/>
+      <c r="E48" s="126"/>
+      <c r="F48" s="137"/>
+      <c r="G48" s="138"/>
+      <c r="H48" s="138"/>
+      <c r="I48" s="139"/>
     </row>
     <row r="49" s="2" customFormat="1" ht="48.75" customHeight="1" spans="1:9">
       <c r="A49" s="44"/>
-      <c r="B49" s="153">
+      <c r="B49" s="151">
         <v>21</v>
       </c>
-      <c r="C49" s="162" t="s">
-        <v>74</v>
-      </c>
-      <c r="D49" s="106"/>
-      <c r="E49" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="F49" s="163" t="s">
-        <v>35</v>
-      </c>
-      <c r="G49" s="144"/>
-      <c r="H49" s="144"/>
-      <c r="I49" s="145"/>
+      <c r="C49" s="160" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" s="104"/>
+      <c r="E49" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="161" t="s">
+        <v>34</v>
+      </c>
+      <c r="G49" s="142"/>
+      <c r="H49" s="142"/>
+      <c r="I49" s="143"/>
     </row>
     <row r="50" s="2" customFormat="1" ht="35.25" customHeight="1" spans="1:9">
       <c r="A50" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B50" s="164">
+        <v>77</v>
+      </c>
+      <c r="B50" s="162">
         <v>22</v>
       </c>
-      <c r="C50" s="111" t="s">
-        <v>76</v>
-      </c>
-      <c r="D50" s="106"/>
-      <c r="E50" s="251" t="s">
+      <c r="C50" s="109" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" s="104"/>
+      <c r="E50" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="161" t="s">
+        <v>34</v>
+      </c>
+      <c r="G50" s="142"/>
+      <c r="H50" s="142"/>
+      <c r="I50" s="143"/>
+    </row>
+    <row r="51" s="2" customFormat="1" ht="42" customHeight="1" spans="1:9">
+      <c r="A51" s="131"/>
+      <c r="B51" s="140">
+        <v>23</v>
+      </c>
+      <c r="C51" s="163" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" s="104"/>
+      <c r="E51" s="248" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="164" t="s">
+        <v>34</v>
+      </c>
+      <c r="G51" s="165"/>
+      <c r="H51" s="165"/>
+      <c r="I51" s="166"/>
+    </row>
+    <row r="52" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
+      <c r="A52" s="131"/>
+      <c r="B52" s="167">
+        <v>24</v>
+      </c>
+      <c r="C52" s="113" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="147"/>
+      <c r="E52" s="168"/>
+      <c r="F52" s="169"/>
+      <c r="G52" s="170"/>
+      <c r="H52" s="170"/>
+      <c r="I52" s="171"/>
+    </row>
+    <row r="53" s="2" customFormat="1" ht="33" customHeight="1" spans="1:9">
+      <c r="A53" s="131"/>
+      <c r="B53" s="146"/>
+      <c r="C53" s="172" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" s="104"/>
+      <c r="E53" s="173"/>
+      <c r="F53" s="133" t="s">
+        <v>34</v>
+      </c>
+      <c r="G53" s="174"/>
+      <c r="H53" s="174"/>
+      <c r="I53" s="175"/>
+    </row>
+    <row r="54" s="2" customFormat="1" ht="23.25" customHeight="1" spans="1:9">
+      <c r="A54" s="131"/>
+      <c r="B54" s="146"/>
+      <c r="C54" s="172" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" s="104"/>
+      <c r="E54" s="173"/>
+      <c r="F54" s="176"/>
+      <c r="G54" s="174"/>
+      <c r="H54" s="174"/>
+      <c r="I54" s="175"/>
+    </row>
+    <row r="55" s="2" customFormat="1" ht="34.5" customHeight="1" spans="1:9">
+      <c r="A55" s="131"/>
+      <c r="B55" s="146"/>
+      <c r="C55" s="172" t="s">
+        <v>83</v>
+      </c>
+      <c r="D55" s="104"/>
+      <c r="E55" s="173"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="174"/>
+      <c r="H55" s="174"/>
+      <c r="I55" s="175"/>
+    </row>
+    <row r="56" s="2" customFormat="1" ht="36.75" customHeight="1" spans="1:9">
+      <c r="A56" s="131"/>
+      <c r="B56" s="146"/>
+      <c r="C56" s="172" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" s="104"/>
+      <c r="E56" s="173"/>
+      <c r="F56" s="176"/>
+      <c r="G56" s="174"/>
+      <c r="H56" s="174"/>
+      <c r="I56" s="175"/>
+    </row>
+    <row r="57" s="2" customFormat="1" ht="40.5" customHeight="1" spans="1:9">
+      <c r="A57" s="131"/>
+      <c r="B57" s="146"/>
+      <c r="C57" s="172" t="s">
+        <v>85</v>
+      </c>
+      <c r="D57" s="104"/>
+      <c r="E57" s="173"/>
+      <c r="F57" s="176"/>
+      <c r="G57" s="174"/>
+      <c r="H57" s="174"/>
+      <c r="I57" s="175"/>
+    </row>
+    <row r="58" s="2" customFormat="1" ht="29.25" customHeight="1" spans="1:9">
+      <c r="A58" s="131"/>
+      <c r="B58" s="151"/>
+      <c r="C58" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D58" s="104"/>
+      <c r="E58" s="173"/>
+      <c r="F58" s="152"/>
+      <c r="G58" s="153"/>
+      <c r="H58" s="153"/>
+      <c r="I58" s="154"/>
+    </row>
+    <row r="59" s="2" customFormat="1" ht="15" customHeight="1" spans="1:9">
+      <c r="A59" s="131"/>
+      <c r="B59" s="146">
+        <v>25</v>
+      </c>
+      <c r="C59" s="172" t="s">
+        <v>87</v>
+      </c>
+      <c r="D59" s="86"/>
+      <c r="E59" s="251" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="G59" s="129"/>
+      <c r="H59" s="129"/>
+      <c r="I59" s="130"/>
+    </row>
+    <row r="60" s="2" customFormat="1" ht="10.8" spans="1:9">
+      <c r="A60" s="131"/>
+      <c r="B60" s="177"/>
+      <c r="C60" s="172" t="s">
+        <v>88</v>
+      </c>
+      <c r="D60" s="98"/>
+      <c r="E60" s="98"/>
+      <c r="F60" s="134"/>
+      <c r="G60" s="134"/>
+      <c r="H60" s="134"/>
+      <c r="I60" s="135"/>
+    </row>
+    <row r="61" s="2" customFormat="1" ht="21.6" spans="1:9">
+      <c r="A61" s="131"/>
+      <c r="B61" s="177"/>
+      <c r="C61" s="132" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61" s="178"/>
+      <c r="E61" s="246" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="134"/>
+      <c r="G61" s="134"/>
+      <c r="H61" s="134"/>
+      <c r="I61" s="135"/>
+    </row>
+    <row r="62" s="2" customFormat="1" ht="21.6" spans="1:9">
+      <c r="A62" s="131"/>
+      <c r="B62" s="179"/>
+      <c r="C62" s="132" t="s">
+        <v>90</v>
+      </c>
+      <c r="D62" s="178"/>
+      <c r="E62" s="246" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="134"/>
+      <c r="G62" s="134"/>
+      <c r="H62" s="134"/>
+      <c r="I62" s="135"/>
+    </row>
+    <row r="63" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
+      <c r="A63" s="131"/>
+      <c r="B63" s="146">
         <v>26</v>
       </c>
-      <c r="F50" s="163" t="s">
-        <v>35</v>
-      </c>
-      <c r="G50" s="144"/>
-      <c r="H50" s="144"/>
-      <c r="I50" s="145"/>
-    </row>
-    <row r="51" s="2" customFormat="1" ht="42" customHeight="1" spans="1:9">
-      <c r="A51" s="133"/>
-      <c r="B51" s="142">
-        <v>23</v>
-      </c>
-      <c r="C51" s="165" t="s">
-        <v>77</v>
-      </c>
-      <c r="D51" s="106"/>
-      <c r="E51" s="251" t="s">
-        <v>26</v>
-      </c>
-      <c r="F51" s="166" t="s">
-        <v>35</v>
-      </c>
-      <c r="G51" s="167"/>
-      <c r="H51" s="167"/>
-      <c r="I51" s="168"/>
-    </row>
-    <row r="52" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A52" s="133"/>
-      <c r="B52" s="169">
-        <v>24</v>
-      </c>
-      <c r="C52" s="113" t="s">
-        <v>78</v>
-      </c>
-      <c r="D52" s="149"/>
-      <c r="E52" s="170"/>
-      <c r="F52" s="171"/>
-      <c r="G52" s="172"/>
-      <c r="H52" s="172"/>
-      <c r="I52" s="173"/>
-    </row>
-    <row r="53" s="2" customFormat="1" ht="33" customHeight="1" spans="1:9">
-      <c r="A53" s="133"/>
-      <c r="B53" s="148"/>
-      <c r="C53" s="174" t="s">
-        <v>79</v>
-      </c>
-      <c r="D53" s="106"/>
-      <c r="E53" s="175"/>
-      <c r="F53" s="135" t="s">
-        <v>35</v>
-      </c>
-      <c r="G53" s="176"/>
-      <c r="H53" s="176"/>
-      <c r="I53" s="177"/>
-    </row>
-    <row r="54" s="2" customFormat="1" ht="23.25" customHeight="1" spans="1:9">
-      <c r="A54" s="133"/>
-      <c r="B54" s="148"/>
-      <c r="C54" s="174" t="s">
-        <v>80</v>
-      </c>
-      <c r="D54" s="106"/>
-      <c r="E54" s="175"/>
-      <c r="F54" s="178"/>
-      <c r="G54" s="176"/>
-      <c r="H54" s="176"/>
-      <c r="I54" s="177"/>
-    </row>
-    <row r="55" s="2" customFormat="1" ht="34.5" customHeight="1" spans="1:9">
-      <c r="A55" s="133"/>
-      <c r="B55" s="148"/>
-      <c r="C55" s="174" t="s">
-        <v>81</v>
-      </c>
-      <c r="D55" s="106"/>
-      <c r="E55" s="175"/>
-      <c r="F55" s="178"/>
-      <c r="G55" s="176"/>
-      <c r="H55" s="176"/>
-      <c r="I55" s="177"/>
-    </row>
-    <row r="56" s="2" customFormat="1" ht="36.75" customHeight="1" spans="1:9">
-      <c r="A56" s="133"/>
-      <c r="B56" s="148"/>
-      <c r="C56" s="174" t="s">
-        <v>82</v>
-      </c>
-      <c r="D56" s="106"/>
-      <c r="E56" s="175"/>
-      <c r="F56" s="178"/>
-      <c r="G56" s="176"/>
-      <c r="H56" s="176"/>
-      <c r="I56" s="177"/>
-    </row>
-    <row r="57" s="2" customFormat="1" ht="40.5" customHeight="1" spans="1:9">
-      <c r="A57" s="133"/>
-      <c r="B57" s="148"/>
-      <c r="C57" s="174" t="s">
-        <v>83</v>
-      </c>
-      <c r="D57" s="106"/>
-      <c r="E57" s="175"/>
-      <c r="F57" s="178"/>
-      <c r="G57" s="176"/>
-      <c r="H57" s="176"/>
-      <c r="I57" s="177"/>
-    </row>
-    <row r="58" s="2" customFormat="1" ht="29.25" customHeight="1" spans="1:9">
-      <c r="A58" s="133"/>
-      <c r="B58" s="153"/>
-      <c r="C58" s="162" t="s">
-        <v>84</v>
-      </c>
-      <c r="D58" s="106"/>
-      <c r="E58" s="175"/>
-      <c r="F58" s="154"/>
-      <c r="G58" s="155"/>
-      <c r="H58" s="155"/>
-      <c r="I58" s="156"/>
-    </row>
-    <row r="59" s="2" customFormat="1" ht="15" customHeight="1" spans="1:9">
-      <c r="A59" s="133"/>
-      <c r="B59" s="148">
+      <c r="C63" s="113" t="s">
+        <v>91</v>
+      </c>
+      <c r="D63" s="86"/>
+      <c r="E63" s="251" t="s">
         <v>25</v>
       </c>
-      <c r="C59" s="174" t="s">
-        <v>85</v>
-      </c>
-      <c r="D59" s="88"/>
-      <c r="E59" s="255" t="s">
-        <v>26</v>
-      </c>
-      <c r="F59" s="131" t="s">
-        <v>35</v>
-      </c>
-      <c r="G59" s="131"/>
-      <c r="H59" s="131"/>
-      <c r="I59" s="132"/>
-    </row>
-    <row r="60" s="2" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A60" s="133"/>
-      <c r="B60" s="179"/>
-      <c r="C60" s="174" t="s">
-        <v>86</v>
-      </c>
-      <c r="D60" s="100"/>
-      <c r="E60" s="100"/>
-      <c r="F60" s="136"/>
-      <c r="G60" s="136"/>
-      <c r="H60" s="136"/>
-      <c r="I60" s="137"/>
-    </row>
-    <row r="61" s="2" customFormat="1" ht="21.6" spans="1:9">
-      <c r="A61" s="133"/>
-      <c r="B61" s="179"/>
-      <c r="C61" s="134" t="s">
-        <v>87</v>
-      </c>
-      <c r="D61" s="180"/>
-      <c r="E61" s="249" t="s">
-        <v>26</v>
-      </c>
-      <c r="F61" s="136"/>
-      <c r="G61" s="136"/>
-      <c r="H61" s="136"/>
-      <c r="I61" s="137"/>
-    </row>
-    <row r="62" s="2" customFormat="1" ht="21.6" spans="1:9">
-      <c r="A62" s="133"/>
-      <c r="B62" s="181"/>
-      <c r="C62" s="134" t="s">
-        <v>88</v>
-      </c>
-      <c r="D62" s="180"/>
-      <c r="E62" s="249" t="s">
-        <v>26</v>
-      </c>
-      <c r="F62" s="136"/>
-      <c r="G62" s="136"/>
-      <c r="H62" s="136"/>
-      <c r="I62" s="137"/>
-    </row>
-    <row r="63" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A63" s="133"/>
-      <c r="B63" s="148">
-        <v>26</v>
-      </c>
-      <c r="C63" s="113" t="s">
-        <v>89</v>
-      </c>
-      <c r="D63" s="88"/>
-      <c r="E63" s="255" t="s">
-        <v>26</v>
-      </c>
-      <c r="F63" s="182"/>
-      <c r="G63" s="183"/>
-      <c r="H63" s="183"/>
-      <c r="I63" s="184"/>
+      <c r="F63" s="180"/>
+      <c r="G63" s="181"/>
+      <c r="H63" s="181"/>
+      <c r="I63" s="182"/>
     </row>
     <row r="64" s="2" customFormat="1" ht="32.25" customHeight="1" spans="1:9">
-      <c r="A64" s="133"/>
-      <c r="B64" s="148"/>
-      <c r="C64" s="138" t="s">
-        <v>90</v>
-      </c>
-      <c r="D64" s="100"/>
-      <c r="E64" s="100"/>
-      <c r="F64" s="182"/>
-      <c r="G64" s="183"/>
-      <c r="H64" s="183"/>
-      <c r="I64" s="184"/>
+      <c r="A64" s="131"/>
+      <c r="B64" s="146"/>
+      <c r="C64" s="136" t="s">
+        <v>92</v>
+      </c>
+      <c r="D64" s="98"/>
+      <c r="E64" s="98"/>
+      <c r="F64" s="180"/>
+      <c r="G64" s="181"/>
+      <c r="H64" s="181"/>
+      <c r="I64" s="182"/>
     </row>
     <row r="65" s="2" customFormat="1" ht="37.5" customHeight="1" spans="1:9">
       <c r="A65" s="44"/>
-      <c r="B65" s="164">
+      <c r="B65" s="162">
         <v>27</v>
       </c>
-      <c r="C65" s="185" t="s">
-        <v>91</v>
-      </c>
-      <c r="D65" s="79"/>
-      <c r="E65" s="249" t="s">
-        <v>26</v>
-      </c>
-      <c r="F65" s="182"/>
-      <c r="G65" s="183"/>
-      <c r="H65" s="183"/>
-      <c r="I65" s="184"/>
+      <c r="C65" s="183" t="s">
+        <v>93</v>
+      </c>
+      <c r="D65" s="77"/>
+      <c r="E65" s="246" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="180"/>
+      <c r="G65" s="181"/>
+      <c r="H65" s="181"/>
+      <c r="I65" s="182"/>
     </row>
     <row r="66" s="2" customFormat="1" ht="32.4" spans="1:9">
       <c r="A66" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="B66" s="186">
+        <v>94</v>
+      </c>
+      <c r="B66" s="184">
         <v>28</v>
       </c>
-      <c r="C66" s="162" t="s">
-        <v>93</v>
-      </c>
-      <c r="D66" s="256" t="s">
-        <v>26</v>
-      </c>
-      <c r="E66" s="188"/>
-      <c r="F66" s="189"/>
-      <c r="G66" s="190"/>
-      <c r="H66" s="190"/>
-      <c r="I66" s="191"/>
+      <c r="C66" s="160" t="s">
+        <v>95</v>
+      </c>
+      <c r="D66" s="252" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="186"/>
+      <c r="F66" s="187"/>
+      <c r="G66" s="188"/>
+      <c r="H66" s="188"/>
+      <c r="I66" s="189"/>
     </row>
     <row r="67" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A67" s="133"/>
-      <c r="B67" s="192">
+      <c r="A67" s="131"/>
+      <c r="B67" s="190">
         <v>29</v>
       </c>
-      <c r="C67" s="193" t="s">
-        <v>94</v>
-      </c>
-      <c r="D67" s="256" t="s">
-        <v>26</v>
-      </c>
-      <c r="E67" s="187"/>
-      <c r="F67" s="163"/>
-      <c r="G67" s="144"/>
-      <c r="H67" s="144"/>
-      <c r="I67" s="145"/>
+      <c r="C67" s="191" t="s">
+        <v>96</v>
+      </c>
+      <c r="D67" s="252" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="185"/>
+      <c r="F67" s="161"/>
+      <c r="G67" s="142"/>
+      <c r="H67" s="142"/>
+      <c r="I67" s="143"/>
     </row>
     <row r="68" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A68" s="133"/>
-      <c r="B68" s="192">
+      <c r="A68" s="131"/>
+      <c r="B68" s="190">
         <v>30</v>
       </c>
-      <c r="C68" s="193" t="s">
-        <v>95</v>
-      </c>
-      <c r="D68" s="256" t="s">
-        <v>26</v>
-      </c>
-      <c r="E68" s="187"/>
-      <c r="F68" s="163"/>
-      <c r="G68" s="144"/>
-      <c r="H68" s="144"/>
-      <c r="I68" s="145"/>
+      <c r="C68" s="191" t="s">
+        <v>97</v>
+      </c>
+      <c r="D68" s="252" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="185"/>
+      <c r="F68" s="161"/>
+      <c r="G68" s="142"/>
+      <c r="H68" s="142"/>
+      <c r="I68" s="143"/>
     </row>
     <row r="69" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A69" s="133"/>
-      <c r="B69" s="192">
+      <c r="A69" s="131"/>
+      <c r="B69" s="190">
         <v>31</v>
       </c>
-      <c r="C69" s="111" t="s">
-        <v>96</v>
-      </c>
-      <c r="D69" s="256" t="s">
-        <v>26</v>
-      </c>
-      <c r="E69" s="187"/>
-      <c r="F69" s="163"/>
-      <c r="G69" s="144"/>
-      <c r="H69" s="144"/>
-      <c r="I69" s="145"/>
+      <c r="C69" s="109" t="s">
+        <v>98</v>
+      </c>
+      <c r="D69" s="252" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="185"/>
+      <c r="F69" s="161"/>
+      <c r="G69" s="142"/>
+      <c r="H69" s="142"/>
+      <c r="I69" s="143"/>
     </row>
     <row r="70" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A70" s="133"/>
-      <c r="B70" s="192">
+      <c r="A70" s="131"/>
+      <c r="B70" s="190">
         <v>32</v>
       </c>
-      <c r="C70" s="111" t="s">
-        <v>97</v>
-      </c>
-      <c r="D70" s="256" t="s">
-        <v>26</v>
-      </c>
-      <c r="E70" s="107"/>
-      <c r="F70" s="163"/>
-      <c r="G70" s="144"/>
-      <c r="H70" s="144"/>
-      <c r="I70" s="145"/>
+      <c r="C70" s="109" t="s">
+        <v>99</v>
+      </c>
+      <c r="D70" s="185"/>
+      <c r="E70" s="105"/>
+      <c r="F70" s="161" t="s">
+        <v>34</v>
+      </c>
+      <c r="G70" s="142"/>
+      <c r="H70" s="142"/>
+      <c r="I70" s="143"/>
     </row>
     <row r="71" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A71" s="133"/>
-      <c r="B71" s="192">
+      <c r="A71" s="131"/>
+      <c r="B71" s="190">
         <v>33</v>
       </c>
-      <c r="C71" s="193" t="s">
-        <v>98</v>
-      </c>
-      <c r="D71" s="107"/>
-      <c r="E71" s="107"/>
-      <c r="F71" s="163" t="s">
-        <v>35</v>
-      </c>
-      <c r="G71" s="144"/>
-      <c r="H71" s="144"/>
-      <c r="I71" s="145"/>
+      <c r="C71" s="191" t="s">
+        <v>100</v>
+      </c>
+      <c r="D71" s="105"/>
+      <c r="E71" s="105"/>
+      <c r="F71" s="161" t="s">
+        <v>34</v>
+      </c>
+      <c r="G71" s="142"/>
+      <c r="H71" s="142"/>
+      <c r="I71" s="143"/>
     </row>
     <row r="72" s="2" customFormat="1" ht="54" spans="1:9">
-      <c r="A72" s="133"/>
-      <c r="B72" s="194">
+      <c r="A72" s="131"/>
+      <c r="B72" s="192">
         <v>34</v>
       </c>
-      <c r="C72" s="195" t="s">
-        <v>99</v>
-      </c>
-      <c r="D72" s="107"/>
-      <c r="E72" s="107"/>
-      <c r="F72" s="163"/>
-      <c r="G72" s="144"/>
-      <c r="H72" s="144"/>
-      <c r="I72" s="145"/>
+      <c r="C72" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="D72" s="105"/>
+      <c r="E72" s="105"/>
+      <c r="F72" s="161" t="s">
+        <v>34</v>
+      </c>
+      <c r="G72" s="142"/>
+      <c r="H72" s="142"/>
+      <c r="I72" s="143"/>
     </row>
     <row r="73" s="2" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A73" s="44"/>
-      <c r="B73" s="196">
+      <c r="B73" s="194">
         <v>35</v>
       </c>
-      <c r="C73" s="197" t="s">
-        <v>100</v>
-      </c>
-      <c r="D73" s="198"/>
-      <c r="E73" s="198"/>
-      <c r="F73" s="199"/>
-      <c r="G73" s="200"/>
-      <c r="H73" s="200"/>
-      <c r="I73" s="201"/>
+      <c r="C73" s="195" t="s">
+        <v>102</v>
+      </c>
+      <c r="D73" s="196"/>
+      <c r="E73" s="196"/>
+      <c r="F73" s="197" t="s">
+        <v>34</v>
+      </c>
+      <c r="G73" s="198"/>
+      <c r="H73" s="198"/>
+      <c r="I73" s="199"/>
     </row>
     <row r="74" s="2" customFormat="1" ht="11.55" spans="1:9">
-      <c r="A74" s="202" t="s">
-        <v>101</v>
-      </c>
-      <c r="B74" s="203"/>
-      <c r="C74" s="204"/>
-      <c r="D74" s="205"/>
-      <c r="E74" s="205"/>
-      <c r="F74" s="204"/>
-      <c r="G74" s="204"/>
-      <c r="H74" s="204"/>
-      <c r="I74" s="204"/>
+      <c r="A74" s="200" t="s">
+        <v>103</v>
+      </c>
+      <c r="B74" s="201"/>
+      <c r="C74" s="202"/>
+      <c r="D74" s="203"/>
+      <c r="E74" s="203"/>
+      <c r="F74" s="202"/>
+      <c r="G74" s="202"/>
+      <c r="H74" s="202"/>
+      <c r="I74" s="202"/>
     </row>
     <row r="75" s="2" customFormat="1" ht="3.75" customHeight="1" spans="1:9">
-      <c r="A75" s="206"/>
-      <c r="B75" s="207"/>
-      <c r="C75" s="208"/>
-      <c r="D75" s="209"/>
-      <c r="E75" s="209"/>
-      <c r="F75" s="209"/>
-      <c r="G75" s="209"/>
-      <c r="H75" s="209"/>
-      <c r="I75" s="210"/>
+      <c r="A75" s="204"/>
+      <c r="B75" s="205"/>
+      <c r="C75" s="206"/>
+      <c r="D75" s="207"/>
+      <c r="E75" s="207"/>
+      <c r="F75" s="207"/>
+      <c r="G75" s="207"/>
+      <c r="H75" s="207"/>
+      <c r="I75" s="208"/>
     </row>
     <row r="76" s="2" customFormat="1" ht="11.4" spans="1:9">
-      <c r="A76" s="211" t="s">
-        <v>102</v>
-      </c>
-      <c r="B76" s="212"/>
-      <c r="I76" s="213"/>
+      <c r="A76" s="209" t="s">
+        <v>104</v>
+      </c>
+      <c r="B76" s="210"/>
+      <c r="I76" s="211"/>
     </row>
     <row r="77" s="2" customFormat="1" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A77" s="214" t="s">
-        <v>103</v>
-      </c>
-      <c r="B77" s="203"/>
-      <c r="I77" s="213"/>
+      <c r="A77" s="212" t="s">
+        <v>105</v>
+      </c>
+      <c r="B77" s="201"/>
+      <c r="I77" s="211"/>
     </row>
     <row r="78" s="2" customFormat="1" ht="10.8" spans="1:9">
-      <c r="A78" s="214" t="s">
-        <v>104</v>
-      </c>
-      <c r="B78" s="203"/>
-      <c r="C78" s="215"/>
-      <c r="D78" s="215"/>
-      <c r="E78" s="215"/>
-      <c r="F78" s="215"/>
-      <c r="G78" s="215"/>
-      <c r="H78" s="215"/>
-      <c r="I78" s="213"/>
+      <c r="A78" s="212" t="s">
+        <v>106</v>
+      </c>
+      <c r="B78" s="201"/>
+      <c r="C78" s="213"/>
+      <c r="D78" s="213"/>
+      <c r="E78" s="213"/>
+      <c r="F78" s="213"/>
+      <c r="G78" s="213"/>
+      <c r="H78" s="213"/>
+      <c r="I78" s="211"/>
     </row>
     <row r="79" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A79" s="216" t="s">
-        <v>105</v>
-      </c>
-      <c r="B79" s="217"/>
-      <c r="F79" s="218"/>
-      <c r="G79" s="218"/>
-      <c r="H79" s="218"/>
-      <c r="I79" s="219"/>
+      <c r="A79" s="214" t="s">
+        <v>107</v>
+      </c>
+      <c r="B79" s="215"/>
+      <c r="F79" s="216"/>
+      <c r="G79" s="216"/>
+      <c r="H79" s="216"/>
+      <c r="I79" s="217"/>
     </row>
     <row r="80" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A80" s="216"/>
-      <c r="B80" s="203"/>
-      <c r="C80" s="203"/>
-      <c r="D80" s="203"/>
-      <c r="E80" s="203"/>
-      <c r="F80" s="203"/>
-      <c r="G80" s="203"/>
-      <c r="H80" s="203"/>
-      <c r="I80" s="213"/>
+      <c r="A80" s="214"/>
+      <c r="B80" s="201"/>
+      <c r="C80" s="201"/>
+      <c r="D80" s="201"/>
+      <c r="E80" s="201"/>
+      <c r="F80" s="201"/>
+      <c r="G80" s="201"/>
+      <c r="H80" s="201"/>
+      <c r="I80" s="211"/>
     </row>
     <row r="81" s="2" customFormat="1" ht="8.25" customHeight="1" spans="1:10">
-      <c r="A81" s="220"/>
-      <c r="B81" s="221"/>
-      <c r="C81" s="222"/>
-      <c r="D81" s="222"/>
-      <c r="E81" s="222"/>
-      <c r="F81" s="222"/>
-      <c r="G81" s="222"/>
-      <c r="H81" s="222"/>
-      <c r="I81" s="223"/>
+      <c r="A81" s="218"/>
+      <c r="B81" s="219"/>
+      <c r="C81" s="220"/>
+      <c r="D81" s="220"/>
+      <c r="E81" s="220"/>
+      <c r="F81" s="220"/>
+      <c r="G81" s="220"/>
+      <c r="H81" s="220"/>
+      <c r="I81" s="221"/>
     </row>
     <row r="82" s="2" customFormat="1" ht="10.8" spans="1:10">
-      <c r="A82" s="224" t="s">
-        <v>106</v>
-      </c>
-      <c r="B82" s="207"/>
-      <c r="C82" s="224" t="s">
-        <v>107</v>
-      </c>
-      <c r="D82" s="224" t="s">
+      <c r="A82" s="222" t="s">
         <v>108</v>
       </c>
-      <c r="E82" s="208"/>
-      <c r="F82" s="208"/>
-      <c r="G82" s="208"/>
-      <c r="H82" s="208"/>
-      <c r="I82" s="210"/>
+      <c r="B82" s="205"/>
+      <c r="C82" s="222" t="s">
+        <v>109</v>
+      </c>
+      <c r="D82" s="222" t="s">
+        <v>110</v>
+      </c>
+      <c r="E82" s="206"/>
+      <c r="F82" s="206"/>
+      <c r="G82" s="206"/>
+      <c r="H82" s="206"/>
+      <c r="I82" s="208"/>
     </row>
     <row r="83" s="2" customFormat="1" ht="9.75" customHeight="1" spans="1:10">
-      <c r="A83" s="216"/>
-      <c r="B83" s="203"/>
-      <c r="C83" s="225"/>
-      <c r="D83" s="225"/>
-      <c r="E83" s="226"/>
-      <c r="F83" s="226"/>
-      <c r="G83" s="226"/>
-      <c r="H83" s="226"/>
-      <c r="I83" s="227"/>
+      <c r="A83" s="214"/>
+      <c r="B83" s="201"/>
+      <c r="C83" s="223"/>
+      <c r="D83" s="223"/>
+      <c r="E83" s="224"/>
+      <c r="F83" s="224"/>
+      <c r="G83" s="224"/>
+      <c r="H83" s="224"/>
+      <c r="I83" s="225"/>
     </row>
     <row r="84" s="2" customFormat="1" ht="15" customHeight="1" spans="1:10">
-      <c r="A84" s="228" t="s">
-        <v>109</v>
-      </c>
-      <c r="B84" s="229"/>
-      <c r="C84" s="228" t="s">
-        <v>110</v>
-      </c>
-      <c r="D84" s="216"/>
-      <c r="E84" s="230" t="s">
+      <c r="A84" s="226" t="s">
         <v>111</v>
       </c>
-      <c r="F84" s="230"/>
-      <c r="G84" s="230"/>
-      <c r="H84" s="230"/>
-      <c r="I84" s="231"/>
-      <c r="J84" s="232"/>
+      <c r="B84" s="227"/>
+      <c r="C84" s="226" t="s">
+        <v>112</v>
+      </c>
+      <c r="D84" s="214"/>
+      <c r="E84" s="228" t="s">
+        <v>113</v>
+      </c>
+      <c r="F84" s="228"/>
+      <c r="G84" s="228"/>
+      <c r="H84" s="228"/>
+      <c r="I84" s="229"/>
+      <c r="J84" s="230"/>
     </row>
     <row r="85" s="3" customFormat="1" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A85" s="233" t="s">
-        <v>112</v>
-      </c>
-      <c r="B85" s="234"/>
-      <c r="C85" s="233" t="s">
-        <v>113</v>
-      </c>
-      <c r="D85" s="233" t="s">
+      <c r="A85" s="231" t="s">
         <v>114</v>
       </c>
-      <c r="E85" s="235"/>
-      <c r="F85" s="235"/>
-      <c r="G85" s="235"/>
-      <c r="H85" s="235"/>
-      <c r="I85" s="234"/>
+      <c r="B85" s="232"/>
+      <c r="C85" s="231" t="s">
+        <v>115</v>
+      </c>
+      <c r="D85" s="231" t="s">
+        <v>116</v>
+      </c>
+      <c r="E85" s="233"/>
+      <c r="F85" s="233"/>
+      <c r="G85" s="233"/>
+      <c r="H85" s="233"/>
+      <c r="I85" s="232"/>
     </row>
     <row r="86" s="3" customFormat="1" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A86" s="236" t="s">
-        <v>115</v>
-      </c>
-      <c r="B86" s="237"/>
-      <c r="C86" s="238" t="s">
-        <v>115</v>
-      </c>
-      <c r="D86" s="239" t="s">
-        <v>115</v>
-      </c>
-      <c r="E86" s="240"/>
-      <c r="F86" s="240"/>
-      <c r="G86" s="240"/>
-      <c r="H86" s="240"/>
-      <c r="I86" s="241"/>
+      <c r="A86" s="234" t="s">
+        <v>117</v>
+      </c>
+      <c r="B86" s="235"/>
+      <c r="C86" s="236" t="s">
+        <v>117</v>
+      </c>
+      <c r="D86" s="237" t="s">
+        <v>117</v>
+      </c>
+      <c r="E86" s="238"/>
+      <c r="F86" s="238"/>
+      <c r="G86" s="238"/>
+      <c r="H86" s="238"/>
+      <c r="I86" s="239"/>
     </row>
     <row r="87" s="2" customFormat="1" ht="12.75" customHeight="1" spans="1:10">
-      <c r="A87" s="242" t="s">
-        <v>116</v>
-      </c>
-      <c r="B87" s="243"/>
+      <c r="A87" s="240"/>
+      <c r="B87" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="92">
@@ -5251,16 +5696,16 @@
     <mergeCell ref="E47:E48"/>
     <mergeCell ref="E59:E60"/>
     <mergeCell ref="E63:E64"/>
-    <mergeCell ref="F53:I58"/>
-    <mergeCell ref="F59:I62"/>
-    <mergeCell ref="F63:I64"/>
+    <mergeCell ref="B9:C10"/>
+    <mergeCell ref="F9:I10"/>
+    <mergeCell ref="F35:I36"/>
     <mergeCell ref="F37:I39"/>
     <mergeCell ref="F42:I43"/>
     <mergeCell ref="F44:I46"/>
     <mergeCell ref="F47:I48"/>
-    <mergeCell ref="F35:I36"/>
-    <mergeCell ref="F9:I10"/>
-    <mergeCell ref="B9:C10"/>
+    <mergeCell ref="F53:I58"/>
+    <mergeCell ref="F59:I62"/>
+    <mergeCell ref="F63:I64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
